--- a/ExtractRules.xlsx
+++ b/ExtractRules.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericpronovost/Doppio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA9A905-0773-7C4B-A388-40EB6A0461C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D77552-66A1-6E46-80A9-316A52F4C73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="2100" windowWidth="30480" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2100" yWindow="3440" windowWidth="29920" windowHeight="18760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtractRules" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ExtractRules!$A$1:$I$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ExtractRules!$A$1:$I$124</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="439">
   <si>
     <t>Area</t>
   </si>
@@ -353,60 +353,36 @@
     <t>CRS181</t>
   </si>
   <si>
-    <t>CSYTAB_CFI1</t>
-  </si>
-  <si>
     <t>CRS181MI</t>
   </si>
   <si>
-    <t>sDSCFI1</t>
-  </si>
-  <si>
     <t>2.17</t>
   </si>
   <si>
     <t>CRS183</t>
   </si>
   <si>
-    <t>CSYTAB_CFI3</t>
-  </si>
-  <si>
     <t>CRS183MI</t>
   </si>
   <si>
-    <t>sDSCFI3</t>
-  </si>
-  <si>
     <t>2.18</t>
   </si>
   <si>
     <t>CRS184</t>
   </si>
   <si>
-    <t>CSYTAB_CFI4</t>
-  </si>
-  <si>
     <t>CRS184MI</t>
   </si>
   <si>
-    <t>sDSCFI4</t>
-  </si>
-  <si>
     <t>2.19</t>
   </si>
   <si>
     <t>CRS185</t>
   </si>
   <si>
-    <t>CSYTAB_CFI5</t>
-  </si>
-  <si>
     <t>CRS185MI</t>
   </si>
   <si>
-    <t>sDSCFI5</t>
-  </si>
-  <si>
     <t>2.20</t>
   </si>
   <si>
@@ -770,9 +746,6 @@
     <t>AddItmType</t>
   </si>
   <si>
-    <t>1000.01</t>
-  </si>
-  <si>
     <t>CRS035</t>
   </si>
   <si>
@@ -1062,6 +1035,324 @@
   </si>
   <si>
     <t>MSPLMX</t>
+  </si>
+  <si>
+    <t>CRS050</t>
+  </si>
+  <si>
+    <t>2.30</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
+    <t>CRS050MI</t>
+  </si>
+  <si>
+    <t>CSYTAB_UNIT</t>
+  </si>
+  <si>
+    <t>sDSUNIT</t>
+  </si>
+  <si>
+    <t>CRS111</t>
+  </si>
+  <si>
+    <t>CRS111MI</t>
+  </si>
+  <si>
+    <t>2.32</t>
+  </si>
+  <si>
+    <t>CEMAIL</t>
+  </si>
+  <si>
+    <t>PDS010</t>
+  </si>
+  <si>
+    <t>CRS080</t>
+  </si>
+  <si>
+    <t>CRS085</t>
+  </si>
+  <si>
+    <t>PDS031</t>
+  </si>
+  <si>
+    <t>PDS033</t>
+  </si>
+  <si>
+    <t>ATS010</t>
+  </si>
+  <si>
+    <t>ATS050</t>
+  </si>
+  <si>
+    <t>PDS050</t>
+  </si>
+  <si>
+    <t>PDS055</t>
+  </si>
+  <si>
+    <t>PMS120</t>
+  </si>
+  <si>
+    <t>CRS785</t>
+  </si>
+  <si>
+    <t>CRS775</t>
+  </si>
+  <si>
+    <t>CRS760</t>
+  </si>
+  <si>
+    <t>CRS585</t>
+  </si>
+  <si>
+    <t>CRS587</t>
+  </si>
+  <si>
+    <t>CRS087</t>
+  </si>
+  <si>
+    <t>CRS787</t>
+  </si>
+  <si>
+    <t>PMS390</t>
+  </si>
+  <si>
+    <t>PDS010MI</t>
+  </si>
+  <si>
+    <t>CRS080MI</t>
+  </si>
+  <si>
+    <t>AddWorkCenter</t>
+  </si>
+  <si>
+    <t>MPDWCT</t>
+  </si>
+  <si>
+    <t>CSYTAB_DEPT</t>
+  </si>
+  <si>
+    <t>sDSDEPT</t>
+  </si>
+  <si>
+    <t>CSYTAB_REAR</t>
+  </si>
+  <si>
+    <t>CRS085WS</t>
+  </si>
+  <si>
+    <t>MPDSHM</t>
+  </si>
+  <si>
+    <t>ATS010MI</t>
+  </si>
+  <si>
+    <t>AddAttribute</t>
+  </si>
+  <si>
+    <t>AddAttrModel</t>
+  </si>
+  <si>
+    <t>ATS050MI</t>
+  </si>
+  <si>
+    <t>PDS050MI</t>
+  </si>
+  <si>
+    <t>PDS055MI</t>
+  </si>
+  <si>
+    <t>AddOrderType</t>
+  </si>
+  <si>
+    <t>PMS120MI</t>
+  </si>
+  <si>
+    <t>MPDSHP</t>
+  </si>
+  <si>
+    <t>MATRMA</t>
+  </si>
+  <si>
+    <t>MAMOHE</t>
+  </si>
+  <si>
+    <t>MPDOPT</t>
+  </si>
+  <si>
+    <t>MPDFHE</t>
+  </si>
+  <si>
+    <t>MWORDT</t>
+  </si>
+  <si>
+    <t>CSYPAR</t>
+  </si>
+  <si>
+    <t>sDSSTRT</t>
+  </si>
+  <si>
+    <t>CSYTAB_STRT</t>
+  </si>
+  <si>
+    <t>sCRS787DS</t>
+  </si>
+  <si>
+    <t>sPMS390DS</t>
+  </si>
+  <si>
+    <t>MPCMPA</t>
+  </si>
+  <si>
+    <t>sCRS585DS</t>
+  </si>
+  <si>
+    <t>sCRS760DS</t>
+  </si>
+  <si>
+    <t>sCRS775DS</t>
+  </si>
+  <si>
+    <t>sCRS785DS</t>
+  </si>
+  <si>
+    <t>OIS010</t>
+  </si>
+  <si>
+    <t>OOTYPE</t>
+  </si>
+  <si>
+    <t>OIS010MI</t>
+  </si>
+  <si>
+    <t>CRS410</t>
+  </si>
+  <si>
+    <t>MNS105</t>
+  </si>
+  <si>
+    <t>CRS012</t>
+  </si>
+  <si>
+    <t>CRS165</t>
+  </si>
+  <si>
+    <t>CRS400</t>
+  </si>
+  <si>
+    <t>CRS910</t>
+  </si>
+  <si>
+    <t>CRS900</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>CRS900MI</t>
+  </si>
+  <si>
+    <t>AddWorkingDays</t>
+  </si>
+  <si>
+    <t>MNS105MI</t>
+  </si>
+  <si>
+    <t>AddLng</t>
+  </si>
+  <si>
+    <t>CSYNBV</t>
+  </si>
+  <si>
+    <t>CMNLNG</t>
+  </si>
+  <si>
+    <t>CSYTAB_LANC</t>
+  </si>
+  <si>
+    <t>sDSLANC</t>
+  </si>
+  <si>
+    <t>CSYNBR</t>
+  </si>
+  <si>
+    <t>CSYNBJ</t>
+  </si>
+  <si>
+    <t>CSYPER</t>
+  </si>
+  <si>
+    <t>CSYCAL</t>
+  </si>
+  <si>
+    <t>MNS410</t>
+  </si>
+  <si>
+    <t>CMNRUS</t>
+  </si>
+  <si>
+    <t>MNS410MI</t>
+  </si>
+  <si>
+    <t>sDSREAR</t>
+  </si>
+  <si>
+    <t>PPS235</t>
+  </si>
+  <si>
+    <t>MPAUTD</t>
+  </si>
+  <si>
+    <t>AddAuthorized</t>
+  </si>
+  <si>
+    <t>PPS235MI</t>
+  </si>
+  <si>
+    <t>2.33</t>
+  </si>
+  <si>
+    <t>sDSCFS1</t>
+  </si>
+  <si>
+    <t>sDSCFS4</t>
+  </si>
+  <si>
+    <t>sDSCFS3</t>
+  </si>
+  <si>
+    <t>sDSCFS5</t>
+  </si>
+  <si>
+    <t>CSYTAB_CFS1</t>
+  </si>
+  <si>
+    <t>CSYTAB_CFS3</t>
+  </si>
+  <si>
+    <t>CSYTAB_CFS4</t>
+  </si>
+  <si>
+    <t>CSYTAB_CFS5</t>
+  </si>
+  <si>
+    <t>2.34</t>
+  </si>
+  <si>
+    <t>PPS110</t>
+  </si>
+  <si>
+    <t>PPS110MI</t>
+  </si>
+  <si>
+    <t>AddPurAgrType</t>
+  </si>
+  <si>
+    <t>MPAGRT</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1400,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1119,6 +1410,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1455,7 +1749,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.1640625" customWidth="1"/>
@@ -1500,22 +1794,22 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
@@ -1529,22 +1823,22 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C3" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="F3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -1553,24 +1847,24 @@
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D4" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -1582,24 +1876,24 @@
         <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D5" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -1616,7 +1910,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
@@ -1645,7 +1939,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>17</v>
@@ -1674,7 +1968,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>20</v>
@@ -1703,7 +1997,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
@@ -1732,7 +2026,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
@@ -1761,71 +2055,71 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B11" s="2">
         <v>1.06</v>
       </c>
       <c r="C11" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D11" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E11" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="F11" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="H11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B12" s="2">
         <v>1.07</v>
       </c>
       <c r="C12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D12" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C13" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="D13" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="F13" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="G13" t="s">
         <v>16</v>
@@ -1839,19 +2133,19 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C14" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="D14" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="E14" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
@@ -1868,19 +2162,19 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="D15" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="E15" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
@@ -1897,22 +2191,22 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C16" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="D16" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="E16" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="F16" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="G16" t="s">
         <v>16</v>
@@ -1926,19 +2220,19 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>275</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C17" t="s">
         <v>284</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C17" t="s">
-        <v>293</v>
-      </c>
       <c r="D17" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E17" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -1946,22 +2240,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C18" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D18" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="E18" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="F18" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -1969,19 +2263,19 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="D19" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="E19" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
@@ -1998,22 +2292,22 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C20" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="D20" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="E20" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="F20" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="G20" t="s">
         <v>16</v>
@@ -2027,19 +2321,19 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C21" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D21" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E21" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -2056,22 +2350,22 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="C22" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E22" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="F22" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="G22" t="s">
         <v>16</v>
@@ -2085,10 +2379,10 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C23" t="s">
         <v>81</v>
@@ -2114,22 +2408,22 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C24" t="s">
+        <v>304</v>
+      </c>
+      <c r="D24" t="s">
+        <v>322</v>
+      </c>
+      <c r="E24" t="s">
+        <v>320</v>
+      </c>
+      <c r="F24" t="s">
         <v>321</v>
-      </c>
-      <c r="C24" t="s">
-        <v>313</v>
-      </c>
-      <c r="D24" t="s">
-        <v>331</v>
-      </c>
-      <c r="E24" t="s">
-        <v>329</v>
-      </c>
-      <c r="F24" t="s">
-        <v>330</v>
       </c>
       <c r="H24" t="s">
         <v>19</v>
@@ -2137,19 +2431,19 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C25" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D25" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="E25" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -2160,19 +2454,19 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C26" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="D26" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E26" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -2183,19 +2477,19 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C27" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="D27" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="E27" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -2206,22 +2500,22 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E28" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F28" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="G28" t="s">
         <v>16</v>
@@ -2230,24 +2524,24 @@
         <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C29" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D29" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="E29" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="H29" t="s">
         <v>19</v>
@@ -2255,19 +2549,19 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C30" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D30" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="E30" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="H30" t="s">
         <v>19</v>
@@ -2275,19 +2569,19 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C31" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="D31" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E31" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -2298,22 +2592,22 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C32" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D32" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E32" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="F32" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G32" t="s">
         <v>16</v>
@@ -2327,22 +2621,22 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D33" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F33" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G33" t="s">
         <v>16</v>
@@ -2356,22 +2650,22 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C34" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D34" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E34" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F34" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="G34" t="s">
         <v>16</v>
@@ -2385,22 +2679,22 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C35" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E35" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F35" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="G35" t="s">
         <v>16</v>
@@ -2414,22 +2708,22 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C36" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D36" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E36" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F36" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="G36" t="s">
         <v>16</v>
@@ -2443,19 +2737,19 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C37" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E37" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F37" t="s">
         <v>13</v>
@@ -2472,22 +2766,22 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C38" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E38" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="F38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="G38" t="s">
         <v>16</v>
@@ -2501,22 +2795,22 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C39" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D39" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E39" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="F39" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G39" t="s">
         <v>16</v>
@@ -2530,19 +2824,19 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C40" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D40" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E40" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F40" t="s">
         <v>13</v>
@@ -2559,22 +2853,22 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C41" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D41" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E41" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F41" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G41" t="s">
         <v>16</v>
@@ -2588,22 +2882,22 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C42" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D42" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E42" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F42" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="G42" t="s">
         <v>16</v>
@@ -2617,22 +2911,22 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C43" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D43" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="E43" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="F43" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="G43" t="s">
         <v>16</v>
@@ -2641,33 +2935,33 @@
         <v>15</v>
       </c>
       <c r="I43" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C44" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D44" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E44" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F44" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G44" t="s">
         <v>16</v>
       </c>
       <c r="H44" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I44" t="s">
         <v>16</v>
@@ -2675,741 +2969,576 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>290</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>244</v>
+        <v>281</v>
+      </c>
+      <c r="B45" s="2">
+        <v>1000.01</v>
       </c>
       <c r="C45" t="s">
-        <v>245</v>
+        <v>188</v>
       </c>
       <c r="D45" t="s">
-        <v>246</v>
+        <v>189</v>
       </c>
       <c r="E45" t="s">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="F45" t="s">
-        <v>248</v>
-      </c>
-      <c r="G45" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
       <c r="H45" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I45" t="s">
-        <v>249</v>
+        <v>192</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>289</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>229</v>
+        <v>281</v>
+      </c>
+      <c r="B46" s="2">
+        <v>1000.02</v>
       </c>
       <c r="C46" t="s">
+        <v>236</v>
+      </c>
+      <c r="D46" t="s">
         <v>237</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>238</v>
       </c>
-      <c r="E46" t="s">
-        <v>237</v>
-      </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>239</v>
       </c>
       <c r="G46" t="s">
         <v>16</v>
       </c>
       <c r="H46" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I46" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>35</v>
+        <v>281</v>
+      </c>
+      <c r="B47" s="2">
+        <v>1000.03</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>343</v>
       </c>
       <c r="D47" t="s">
-        <v>37</v>
+        <v>364</v>
       </c>
       <c r="E47" t="s">
-        <v>38</v>
+        <v>361</v>
       </c>
       <c r="F47" t="s">
-        <v>39</v>
-      </c>
-      <c r="G47" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="H47" t="s">
-        <v>19</v>
-      </c>
-      <c r="I47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>40</v>
+        <v>281</v>
+      </c>
+      <c r="B48" s="2">
+        <v>1000.04</v>
       </c>
       <c r="C48" t="s">
-        <v>41</v>
+        <v>344</v>
       </c>
       <c r="D48" t="s">
-        <v>42</v>
+        <v>365</v>
       </c>
       <c r="E48" t="s">
-        <v>38</v>
+        <v>362</v>
       </c>
       <c r="F48" t="s">
-        <v>39</v>
-      </c>
-      <c r="G48" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H48" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I48" t="s">
-        <v>16</v>
+        <v>366</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>34</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>43</v>
+        <v>281</v>
+      </c>
+      <c r="B49" s="2">
+        <v>1000.05</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>345</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>367</v>
       </c>
       <c r="E49" t="s">
-        <v>38</v>
+        <v>368</v>
       </c>
       <c r="F49" t="s">
-        <v>23</v>
-      </c>
-      <c r="G49" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H49" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I49" t="s">
-        <v>16</v>
+        <v>420</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>34</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>46</v>
+        <v>281</v>
+      </c>
+      <c r="B50" s="2">
+        <v>1000.06</v>
       </c>
       <c r="C50" t="s">
-        <v>47</v>
+        <v>346</v>
       </c>
       <c r="D50" t="s">
-        <v>48</v>
-      </c>
-      <c r="E50" t="s">
-        <v>38</v>
-      </c>
-      <c r="F50" t="s">
-        <v>49</v>
-      </c>
-      <c r="G50" t="s">
-        <v>16</v>
+        <v>369</v>
       </c>
       <c r="H50" t="s">
-        <v>19</v>
-      </c>
-      <c r="I50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>34</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>50</v>
+        <v>281</v>
+      </c>
+      <c r="B51" s="2">
+        <v>1000.07</v>
       </c>
       <c r="C51" t="s">
-        <v>51</v>
+        <v>347</v>
       </c>
       <c r="D51" t="s">
-        <v>52</v>
-      </c>
-      <c r="E51" t="s">
-        <v>51</v>
-      </c>
-      <c r="F51" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51" t="s">
-        <v>16</v>
+        <v>378</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
-      </c>
-      <c r="I51" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>34</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>54</v>
+        <v>281</v>
+      </c>
+      <c r="B52" s="2">
+        <v>1000.08</v>
       </c>
       <c r="C52" t="s">
-        <v>55</v>
+        <v>348</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>379</v>
       </c>
       <c r="E52" t="s">
-        <v>57</v>
+        <v>370</v>
       </c>
       <c r="F52" t="s">
-        <v>58</v>
-      </c>
-      <c r="G52" t="s">
-        <v>16</v>
+        <v>371</v>
       </c>
       <c r="H52" t="s">
-        <v>19</v>
-      </c>
-      <c r="I52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>34</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>59</v>
+        <v>281</v>
+      </c>
+      <c r="B53" s="2">
+        <v>1000.09</v>
       </c>
       <c r="C53" t="s">
-        <v>60</v>
+        <v>349</v>
       </c>
       <c r="D53" t="s">
-        <v>61</v>
+        <v>380</v>
       </c>
       <c r="E53" t="s">
-        <v>62</v>
+        <v>373</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
-      </c>
-      <c r="G53" t="s">
-        <v>16</v>
+        <v>372</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
-      </c>
-      <c r="I53" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>34</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>64</v>
+        <v>281</v>
+      </c>
+      <c r="B54" s="4">
+        <v>1000.1</v>
       </c>
       <c r="C54" t="s">
-        <v>230</v>
+        <v>350</v>
       </c>
       <c r="D54" t="s">
-        <v>231</v>
+        <v>381</v>
       </c>
       <c r="E54" t="s">
-        <v>232</v>
+        <v>374</v>
       </c>
       <c r="F54" t="s">
-        <v>16</v>
-      </c>
-      <c r="G54" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>34</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>70</v>
+        <v>281</v>
+      </c>
+      <c r="B55" s="2">
+        <v>1000.11</v>
       </c>
       <c r="C55" t="s">
-        <v>65</v>
+        <v>351</v>
       </c>
       <c r="D55" t="s">
-        <v>66</v>
+        <v>382</v>
       </c>
       <c r="E55" t="s">
-        <v>67</v>
+        <v>375</v>
       </c>
       <c r="F55" t="s">
-        <v>68</v>
-      </c>
-      <c r="G55" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
-      </c>
-      <c r="I55" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>34</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>74</v>
+        <v>281</v>
+      </c>
+      <c r="B56" s="2">
+        <v>1000.12</v>
       </c>
       <c r="C56" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="D56" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="E56" t="s">
-        <v>71</v>
+        <v>178</v>
       </c>
       <c r="F56" t="s">
-        <v>16</v>
-      </c>
-      <c r="G56" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
-      </c>
-      <c r="I56" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>34</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>80</v>
+        <v>281</v>
+      </c>
+      <c r="B57" s="2">
+        <v>1000.13</v>
       </c>
       <c r="C57" t="s">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="D57" t="s">
-        <v>76</v>
+        <v>181</v>
       </c>
       <c r="E57" t="s">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="F57" t="s">
-        <v>78</v>
-      </c>
-      <c r="G57" t="s">
-        <v>16</v>
+        <v>183</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
-      </c>
-      <c r="I57" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>34</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>86</v>
+        <v>281</v>
+      </c>
+      <c r="B58" s="2">
+        <v>1000.14</v>
       </c>
       <c r="C58" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="D58" t="s">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="E58" t="s">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="F58" t="s">
-        <v>84</v>
-      </c>
-      <c r="G58" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
-      </c>
-      <c r="I58" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>34</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>90</v>
+        <v>281</v>
+      </c>
+      <c r="B59" s="2">
+        <v>1000.15</v>
       </c>
       <c r="C59" t="s">
-        <v>87</v>
+        <v>352</v>
       </c>
       <c r="D59" t="s">
-        <v>88</v>
+        <v>383</v>
       </c>
       <c r="E59" t="s">
-        <v>87</v>
+        <v>377</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
-      </c>
-      <c r="G59" t="s">
-        <v>16</v>
+        <v>376</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
-      </c>
-      <c r="I59" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>34</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>95</v>
+        <v>281</v>
+      </c>
+      <c r="B60" s="2">
+        <v>1000.16</v>
       </c>
       <c r="C60" t="s">
-        <v>91</v>
+        <v>353</v>
       </c>
       <c r="D60" t="s">
-        <v>92</v>
-      </c>
-      <c r="E60" t="s">
-        <v>93</v>
-      </c>
-      <c r="F60" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" t="s">
-        <v>16</v>
+        <v>384</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
       </c>
       <c r="I60" t="s">
-        <v>94</v>
+        <v>393</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>34</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>99</v>
+        <v>281</v>
+      </c>
+      <c r="B61" s="2">
+        <v>1000.17</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>354</v>
       </c>
       <c r="D61" t="s">
-        <v>97</v>
-      </c>
-      <c r="E61" t="s">
-        <v>96</v>
-      </c>
-      <c r="F61" t="s">
-        <v>16</v>
-      </c>
-      <c r="G61" t="s">
-        <v>16</v>
+        <v>384</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
       </c>
       <c r="I61" t="s">
-        <v>98</v>
+        <v>392</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>34</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>103</v>
+        <v>281</v>
+      </c>
+      <c r="B62" s="2">
+        <v>1000.18</v>
       </c>
       <c r="C62" t="s">
-        <v>100</v>
+        <v>355</v>
       </c>
       <c r="D62" t="s">
-        <v>101</v>
-      </c>
-      <c r="E62" t="s">
-        <v>100</v>
-      </c>
-      <c r="F62" t="s">
-        <v>16</v>
-      </c>
-      <c r="G62" t="s">
-        <v>16</v>
+        <v>384</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
       </c>
       <c r="I62" t="s">
-        <v>102</v>
+        <v>391</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>34</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>108</v>
+        <v>281</v>
+      </c>
+      <c r="B63" s="2">
+        <v>1000.19</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>356</v>
       </c>
       <c r="D63" t="s">
-        <v>105</v>
-      </c>
-      <c r="E63" t="s">
-        <v>106</v>
-      </c>
-      <c r="F63" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" t="s">
-        <v>16</v>
+        <v>384</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
       </c>
       <c r="I63" t="s">
-        <v>107</v>
+        <v>390</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>34</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>113</v>
+        <v>281</v>
+      </c>
+      <c r="B64" s="4">
+        <v>1000.2</v>
       </c>
       <c r="C64" t="s">
-        <v>109</v>
+        <v>357</v>
       </c>
       <c r="D64" t="s">
-        <v>110</v>
-      </c>
-      <c r="E64" t="s">
-        <v>111</v>
-      </c>
-      <c r="F64" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" t="s">
-        <v>16</v>
+        <v>389</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
-      </c>
-      <c r="I64" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>34</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>118</v>
+        <v>281</v>
+      </c>
+      <c r="B65" s="2">
+        <v>1000.21</v>
       </c>
       <c r="C65" t="s">
-        <v>114</v>
+        <v>358</v>
       </c>
       <c r="D65" t="s">
-        <v>115</v>
-      </c>
-      <c r="E65" t="s">
-        <v>116</v>
-      </c>
-      <c r="F65" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" t="s">
-        <v>16</v>
+        <v>386</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
       </c>
       <c r="I65" t="s">
-        <v>117</v>
+        <v>385</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>34</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>123</v>
+        <v>281</v>
+      </c>
+      <c r="B66" s="2">
+        <v>1000.22</v>
       </c>
       <c r="C66" t="s">
-        <v>119</v>
+        <v>359</v>
       </c>
       <c r="D66" t="s">
-        <v>120</v>
-      </c>
-      <c r="E66" t="s">
-        <v>121</v>
-      </c>
-      <c r="F66" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" t="s">
-        <v>16</v>
+        <v>384</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
       </c>
       <c r="I66" t="s">
-        <v>122</v>
+        <v>387</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>34</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>129</v>
+        <v>281</v>
+      </c>
+      <c r="B67" s="2">
+        <v>1000.23</v>
       </c>
       <c r="C67" t="s">
-        <v>124</v>
+        <v>360</v>
       </c>
       <c r="D67" t="s">
-        <v>125</v>
-      </c>
-      <c r="E67" t="s">
-        <v>126</v>
-      </c>
-      <c r="F67" t="s">
-        <v>127</v>
-      </c>
-      <c r="G67" t="s">
-        <v>16</v>
+        <v>384</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
       </c>
       <c r="I67" t="s">
-        <v>128</v>
+        <v>388</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>34</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>133</v>
+        <v>281</v>
+      </c>
+      <c r="B68" s="2">
+        <v>1000.24</v>
       </c>
       <c r="C68" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="D68" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E68" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="F68" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="G68" t="s">
         <v>16</v>
       </c>
       <c r="H68" t="s">
-        <v>19</v>
-      </c>
-      <c r="I68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>34</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>137</v>
+        <v>281</v>
+      </c>
+      <c r="B69" s="2">
+        <v>1000.25</v>
       </c>
       <c r="C69" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="D69" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="E69" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="G69" t="s">
         <v>16</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
-      </c>
-      <c r="I69" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>34</v>
+        <v>280</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>140</v>
+        <v>221</v>
       </c>
       <c r="C70" t="s">
-        <v>138</v>
+        <v>229</v>
       </c>
       <c r="D70" t="s">
-        <v>139</v>
+        <v>230</v>
       </c>
       <c r="E70" t="s">
-        <v>138</v>
+        <v>229</v>
       </c>
       <c r="F70" t="s">
         <v>16</v>
@@ -3429,19 +3558,19 @@
         <v>34</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="C71" t="s">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="D71" t="s">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="E71" t="s">
-        <v>141</v>
+        <v>38</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G71" t="s">
         <v>16</v>
@@ -3458,19 +3587,19 @@
         <v>34</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>148</v>
+        <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>144</v>
+        <v>41</v>
       </c>
       <c r="D72" t="s">
-        <v>145</v>
+        <v>42</v>
       </c>
       <c r="E72" t="s">
-        <v>146</v>
+        <v>38</v>
       </c>
       <c r="F72" t="s">
-        <v>147</v>
+        <v>39</v>
       </c>
       <c r="G72" t="s">
         <v>16</v>
@@ -3487,19 +3616,19 @@
         <v>34</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>299</v>
+        <v>43</v>
       </c>
       <c r="C73" t="s">
-        <v>149</v>
+        <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="E73" t="s">
-        <v>146</v>
+        <v>38</v>
       </c>
       <c r="F73" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="G73" t="s">
         <v>16</v>
@@ -3516,25 +3645,28 @@
         <v>34</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>300</v>
+        <v>46</v>
       </c>
       <c r="C74" t="s">
-        <v>158</v>
+        <v>47</v>
       </c>
       <c r="D74" t="s">
-        <v>159</v>
+        <v>48</v>
       </c>
       <c r="E74" t="s">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="F74" t="s">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="G74" t="s">
         <v>16</v>
       </c>
       <c r="H74" t="s">
         <v>19</v>
+      </c>
+      <c r="I74" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -3542,22 +3674,19 @@
         <v>34</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>301</v>
+        <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>225</v>
+        <v>339</v>
       </c>
       <c r="D75" t="s">
-        <v>226</v>
+        <v>342</v>
       </c>
       <c r="E75" t="s">
-        <v>227</v>
+        <v>340</v>
       </c>
       <c r="F75" t="s">
-        <v>228</v>
-      </c>
-      <c r="G75" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H75" t="s">
         <v>19</v>
@@ -3565,51 +3694,51 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>286</v>
+        <v>34</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>216</v>
+        <v>54</v>
       </c>
       <c r="C76" t="s">
-        <v>217</v>
+        <v>51</v>
       </c>
       <c r="D76" t="s">
-        <v>218</v>
+        <v>52</v>
       </c>
       <c r="E76" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
       <c r="F76" t="s">
-        <v>220</v>
+        <v>16</v>
       </c>
       <c r="G76" t="s">
         <v>16</v>
       </c>
       <c r="H76" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I76" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>286</v>
+        <v>34</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>221</v>
+        <v>59</v>
       </c>
       <c r="C77" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="D77" t="s">
-        <v>222</v>
+        <v>56</v>
       </c>
       <c r="E77" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="F77" t="s">
-        <v>223</v>
+        <v>58</v>
       </c>
       <c r="G77" t="s">
         <v>16</v>
@@ -3623,158 +3752,1197 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>286</v>
+        <v>34</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>224</v>
+        <v>64</v>
       </c>
       <c r="C78" t="s">
-        <v>225</v>
+        <v>60</v>
       </c>
       <c r="D78" t="s">
-        <v>226</v>
+        <v>61</v>
       </c>
       <c r="E78" t="s">
-        <v>227</v>
+        <v>62</v>
       </c>
       <c r="F78" t="s">
-        <v>228</v>
+        <v>16</v>
       </c>
       <c r="G78" t="s">
         <v>16</v>
       </c>
       <c r="H78" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I78" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>307</v>
-      </c>
-      <c r="B79" s="2">
-        <v>6.01</v>
+        <v>34</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C79" t="s">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="D79" t="s">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="E79" t="s">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="F79" t="s">
-        <v>78</v>
+        <v>16</v>
+      </c>
+      <c r="G79" t="s">
+        <v>16</v>
       </c>
       <c r="H79" t="s">
         <v>19</v>
       </c>
-      <c r="I79" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>307</v>
-      </c>
-      <c r="B80" s="2">
-        <v>6.02</v>
+        <v>34</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C80" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D80" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E80" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="F80" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="G80" t="s">
         <v>16</v>
       </c>
       <c r="H80" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I80" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>307</v>
-      </c>
-      <c r="B81" s="2">
-        <v>6.03</v>
+        <v>34</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="D81" t="s">
-        <v>214</v>
+        <v>72</v>
       </c>
       <c r="E81" t="s">
-        <v>213</v>
+        <v>71</v>
+      </c>
+      <c r="F81" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" t="s">
+        <v>16</v>
       </c>
       <c r="H81" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I81" t="s">
-        <v>215</v>
+        <v>73</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>307</v>
-      </c>
-      <c r="B82" s="2">
-        <v>6.04</v>
+        <v>34</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>308</v>
+        <v>75</v>
       </c>
       <c r="D82" t="s">
-        <v>311</v>
+        <v>76</v>
       </c>
       <c r="E82" t="s">
-        <v>308</v>
+        <v>77</v>
+      </c>
+      <c r="F82" t="s">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s">
+        <v>16</v>
       </c>
       <c r="H82" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I82" t="s">
-        <v>312</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>307</v>
-      </c>
-      <c r="B83" s="2">
+        <v>34</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C83" t="s">
+        <v>81</v>
+      </c>
+      <c r="D83" t="s">
+        <v>82</v>
+      </c>
+      <c r="E83" t="s">
+        <v>83</v>
+      </c>
+      <c r="F83" t="s">
+        <v>84</v>
+      </c>
+      <c r="G83" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>34</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C84" t="s">
+        <v>87</v>
+      </c>
+      <c r="D84" t="s">
+        <v>88</v>
+      </c>
+      <c r="E84" t="s">
+        <v>87</v>
+      </c>
+      <c r="F84" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>34</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C85" t="s">
+        <v>91</v>
+      </c>
+      <c r="D85" t="s">
+        <v>92</v>
+      </c>
+      <c r="E85" t="s">
+        <v>93</v>
+      </c>
+      <c r="F85" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" t="s">
+        <v>16</v>
+      </c>
+      <c r="H85" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>34</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C86" t="s">
+        <v>96</v>
+      </c>
+      <c r="D86" t="s">
+        <v>97</v>
+      </c>
+      <c r="E86" t="s">
+        <v>96</v>
+      </c>
+      <c r="F86" t="s">
+        <v>16</v>
+      </c>
+      <c r="G86" t="s">
+        <v>16</v>
+      </c>
+      <c r="H86" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>34</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C87" t="s">
+        <v>100</v>
+      </c>
+      <c r="D87" t="s">
+        <v>101</v>
+      </c>
+      <c r="E87" t="s">
+        <v>100</v>
+      </c>
+      <c r="F87" t="s">
+        <v>16</v>
+      </c>
+      <c r="G87" t="s">
+        <v>16</v>
+      </c>
+      <c r="H87" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>34</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C88" t="s">
+        <v>104</v>
+      </c>
+      <c r="D88" t="s">
+        <v>430</v>
+      </c>
+      <c r="E88" t="s">
+        <v>105</v>
+      </c>
+      <c r="F88" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" t="s">
+        <v>16</v>
+      </c>
+      <c r="H88" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>34</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C89" t="s">
+        <v>107</v>
+      </c>
+      <c r="D89" t="s">
+        <v>431</v>
+      </c>
+      <c r="E89" t="s">
+        <v>108</v>
+      </c>
+      <c r="F89" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>34</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C90" t="s">
+        <v>110</v>
+      </c>
+      <c r="D90" t="s">
+        <v>432</v>
+      </c>
+      <c r="E90" t="s">
+        <v>111</v>
+      </c>
+      <c r="F90" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" t="s">
+        <v>16</v>
+      </c>
+      <c r="H90" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>34</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C91" t="s">
+        <v>113</v>
+      </c>
+      <c r="D91" t="s">
+        <v>433</v>
+      </c>
+      <c r="E91" t="s">
+        <v>114</v>
+      </c>
+      <c r="F91" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>34</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C92" t="s">
+        <v>116</v>
+      </c>
+      <c r="D92" t="s">
+        <v>117</v>
+      </c>
+      <c r="E92" t="s">
+        <v>118</v>
+      </c>
+      <c r="F92" t="s">
+        <v>119</v>
+      </c>
+      <c r="G92" t="s">
+        <v>16</v>
+      </c>
+      <c r="H92" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>34</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C93" t="s">
+        <v>122</v>
+      </c>
+      <c r="D93" t="s">
+        <v>123</v>
+      </c>
+      <c r="E93" t="s">
+        <v>124</v>
+      </c>
+      <c r="F93" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" t="s">
+        <v>16</v>
+      </c>
+      <c r="H93" t="s">
+        <v>19</v>
+      </c>
+      <c r="I93" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>34</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C94" t="s">
+        <v>126</v>
+      </c>
+      <c r="D94" t="s">
+        <v>127</v>
+      </c>
+      <c r="E94" t="s">
+        <v>126</v>
+      </c>
+      <c r="F94" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>34</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C95" t="s">
+        <v>130</v>
+      </c>
+      <c r="D95" t="s">
+        <v>131</v>
+      </c>
+      <c r="E95" t="s">
+        <v>130</v>
+      </c>
+      <c r="F95" t="s">
+        <v>16</v>
+      </c>
+      <c r="G95" t="s">
+        <v>16</v>
+      </c>
+      <c r="H95" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>34</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C96" t="s">
+        <v>133</v>
+      </c>
+      <c r="D96" t="s">
+        <v>134</v>
+      </c>
+      <c r="E96" t="s">
+        <v>133</v>
+      </c>
+      <c r="F96" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>34</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C97" t="s">
+        <v>421</v>
+      </c>
+      <c r="D97" t="s">
+        <v>422</v>
+      </c>
+      <c r="E97" t="s">
+        <v>424</v>
+      </c>
+      <c r="F97" t="s">
+        <v>423</v>
+      </c>
+      <c r="H97" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>34</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C98" t="s">
+        <v>136</v>
+      </c>
+      <c r="D98" t="s">
+        <v>137</v>
+      </c>
+      <c r="E98" t="s">
+        <v>138</v>
+      </c>
+      <c r="F98" t="s">
+        <v>139</v>
+      </c>
+      <c r="G98" t="s">
+        <v>16</v>
+      </c>
+      <c r="H98" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>34</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C99" t="s">
+        <v>141</v>
+      </c>
+      <c r="D99" t="s">
+        <v>142</v>
+      </c>
+      <c r="E99" t="s">
+        <v>138</v>
+      </c>
+      <c r="F99" t="s">
+        <v>143</v>
+      </c>
+      <c r="G99" t="s">
+        <v>16</v>
+      </c>
+      <c r="H99" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>34</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C100" t="s">
+        <v>150</v>
+      </c>
+      <c r="D100" t="s">
+        <v>151</v>
+      </c>
+      <c r="E100" t="s">
+        <v>147</v>
+      </c>
+      <c r="F100" t="s">
+        <v>152</v>
+      </c>
+      <c r="G100" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>34</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" t="s">
+        <v>217</v>
+      </c>
+      <c r="D101" t="s">
+        <v>218</v>
+      </c>
+      <c r="E101" t="s">
+        <v>219</v>
+      </c>
+      <c r="F101" t="s">
+        <v>220</v>
+      </c>
+      <c r="G101" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>34</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C102" t="s">
+        <v>163</v>
+      </c>
+      <c r="D102" t="s">
+        <v>164</v>
+      </c>
+      <c r="E102" t="s">
+        <v>165</v>
+      </c>
+      <c r="F102" t="s">
+        <v>13</v>
+      </c>
+      <c r="H102" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>34</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C103" t="s">
+        <v>333</v>
+      </c>
+      <c r="D103" t="s">
+        <v>337</v>
+      </c>
+      <c r="E103" t="s">
+        <v>336</v>
+      </c>
+      <c r="F103" t="s">
+        <v>13</v>
+      </c>
+      <c r="H103" t="s">
+        <v>15</v>
+      </c>
+      <c r="I103" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>34</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C104" t="s">
+        <v>435</v>
+      </c>
+      <c r="D104" t="s">
+        <v>438</v>
+      </c>
+      <c r="E104" t="s">
+        <v>436</v>
+      </c>
+      <c r="F104" t="s">
+        <v>437</v>
+      </c>
+      <c r="H104" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>277</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C105" t="s">
+        <v>209</v>
+      </c>
+      <c r="D105" t="s">
+        <v>210</v>
+      </c>
+      <c r="E105" t="s">
+        <v>211</v>
+      </c>
+      <c r="F105" t="s">
+        <v>212</v>
+      </c>
+      <c r="G105" t="s">
+        <v>16</v>
+      </c>
+      <c r="H105" t="s">
+        <v>19</v>
+      </c>
+      <c r="I105" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>277</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C106" t="s">
+        <v>209</v>
+      </c>
+      <c r="D106" t="s">
+        <v>214</v>
+      </c>
+      <c r="E106" t="s">
+        <v>211</v>
+      </c>
+      <c r="F106" t="s">
+        <v>215</v>
+      </c>
+      <c r="G106" t="s">
+        <v>16</v>
+      </c>
+      <c r="H106" t="s">
+        <v>19</v>
+      </c>
+      <c r="I106" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>277</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C107" t="s">
+        <v>217</v>
+      </c>
+      <c r="D107" t="s">
+        <v>218</v>
+      </c>
+      <c r="E107" t="s">
+        <v>219</v>
+      </c>
+      <c r="F107" t="s">
+        <v>220</v>
+      </c>
+      <c r="G107" t="s">
+        <v>16</v>
+      </c>
+      <c r="H107" t="s">
+        <v>19</v>
+      </c>
+      <c r="I107" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>298</v>
+      </c>
+      <c r="B108" s="2">
+        <v>6.01</v>
+      </c>
+      <c r="C108" t="s">
+        <v>75</v>
+      </c>
+      <c r="D108" t="s">
+        <v>76</v>
+      </c>
+      <c r="E108" t="s">
+        <v>77</v>
+      </c>
+      <c r="F108" t="s">
+        <v>78</v>
+      </c>
+      <c r="H108" t="s">
+        <v>15</v>
+      </c>
+      <c r="I108" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>298</v>
+      </c>
+      <c r="B109" s="2">
+        <v>6.02</v>
+      </c>
+      <c r="C109" t="s">
+        <v>81</v>
+      </c>
+      <c r="D109" t="s">
+        <v>82</v>
+      </c>
+      <c r="E109" t="s">
+        <v>83</v>
+      </c>
+      <c r="F109" t="s">
+        <v>84</v>
+      </c>
+      <c r="G109" t="s">
+        <v>16</v>
+      </c>
+      <c r="H109" t="s">
+        <v>15</v>
+      </c>
+      <c r="I109" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>298</v>
+      </c>
+      <c r="B110" s="2">
+        <v>6.03</v>
+      </c>
+      <c r="C110" t="s">
+        <v>205</v>
+      </c>
+      <c r="D110" t="s">
+        <v>206</v>
+      </c>
+      <c r="E110" t="s">
+        <v>205</v>
+      </c>
+      <c r="H110" t="s">
+        <v>15</v>
+      </c>
+      <c r="I110" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>298</v>
+      </c>
+      <c r="B111" s="2">
+        <v>6.04</v>
+      </c>
+      <c r="C111" t="s">
+        <v>299</v>
+      </c>
+      <c r="D111" t="s">
+        <v>302</v>
+      </c>
+      <c r="E111" t="s">
+        <v>299</v>
+      </c>
+      <c r="H111" t="s">
+        <v>15</v>
+      </c>
+      <c r="I111" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>298</v>
+      </c>
+      <c r="B112" s="2">
         <v>6.05</v>
       </c>
-      <c r="C83" t="s">
-        <v>309</v>
-      </c>
-      <c r="D83" t="s">
-        <v>310</v>
-      </c>
-      <c r="E83" t="s">
-        <v>309</v>
-      </c>
-      <c r="H83" t="s">
+      <c r="C112" t="s">
+        <v>300</v>
+      </c>
+      <c r="D112" t="s">
+        <v>301</v>
+      </c>
+      <c r="E112" t="s">
+        <v>300</v>
+      </c>
+      <c r="H112" t="s">
         <v>19</v>
       </c>
     </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>298</v>
+      </c>
+      <c r="B113" s="2">
+        <v>6.06</v>
+      </c>
+      <c r="C113" t="s">
+        <v>394</v>
+      </c>
+      <c r="D113" t="s">
+        <v>395</v>
+      </c>
+      <c r="E113" t="s">
+        <v>396</v>
+      </c>
+      <c r="F113" t="s">
+        <v>13</v>
+      </c>
+      <c r="H113" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>404</v>
+      </c>
+      <c r="B114" s="2">
+        <v>7.01</v>
+      </c>
+      <c r="C114" t="s">
+        <v>397</v>
+      </c>
+      <c r="D114" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>404</v>
+      </c>
+      <c r="B115" s="2">
+        <v>7.02</v>
+      </c>
+      <c r="C115" t="s">
+        <v>398</v>
+      </c>
+      <c r="D115" t="s">
+        <v>410</v>
+      </c>
+      <c r="E115" t="s">
+        <v>407</v>
+      </c>
+      <c r="F115" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>404</v>
+      </c>
+      <c r="B116" s="2">
+        <v>7.03</v>
+      </c>
+      <c r="C116" t="s">
+        <v>51</v>
+      </c>
+      <c r="D116" t="s">
+        <v>52</v>
+      </c>
+      <c r="E116" t="s">
+        <v>51</v>
+      </c>
+      <c r="F116" t="s">
+        <v>16</v>
+      </c>
+      <c r="G116" t="s">
+        <v>16</v>
+      </c>
+      <c r="H116" t="s">
+        <v>15</v>
+      </c>
+      <c r="I116" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>404</v>
+      </c>
+      <c r="B117" s="2">
+        <v>7.04</v>
+      </c>
+      <c r="C117" t="s">
+        <v>399</v>
+      </c>
+      <c r="D117" t="s">
+        <v>411</v>
+      </c>
+      <c r="H117" t="s">
+        <v>15</v>
+      </c>
+      <c r="I117" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>404</v>
+      </c>
+      <c r="B118" s="2">
+        <v>7.05</v>
+      </c>
+      <c r="C118" t="s">
+        <v>91</v>
+      </c>
+      <c r="D118" t="s">
+        <v>92</v>
+      </c>
+      <c r="E118" t="s">
+        <v>93</v>
+      </c>
+      <c r="F118" t="s">
+        <v>13</v>
+      </c>
+      <c r="H118" t="s">
+        <v>15</v>
+      </c>
+      <c r="I118" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>404</v>
+      </c>
+      <c r="B119" s="2">
+        <v>7.06</v>
+      </c>
+      <c r="C119" t="s">
+        <v>400</v>
+      </c>
+      <c r="D119" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>404</v>
+      </c>
+      <c r="B120" s="2">
+        <v>7.07</v>
+      </c>
+      <c r="C120" t="s">
+        <v>417</v>
+      </c>
+      <c r="D120" t="s">
+        <v>418</v>
+      </c>
+      <c r="E120" t="s">
+        <v>419</v>
+      </c>
+      <c r="F120" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>404</v>
+      </c>
+      <c r="B121" s="2">
+        <v>7.08</v>
+      </c>
+      <c r="C121" t="s">
+        <v>401</v>
+      </c>
+      <c r="D121" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>404</v>
+      </c>
+      <c r="B122" s="2">
+        <v>7.09</v>
+      </c>
+      <c r="C122" t="s">
+        <v>397</v>
+      </c>
+      <c r="D122" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>404</v>
+      </c>
+      <c r="B123" s="4">
+        <v>7.1</v>
+      </c>
+      <c r="C123" t="s">
+        <v>402</v>
+      </c>
+      <c r="D123" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>404</v>
+      </c>
+      <c r="B124" s="2">
+        <v>7.11</v>
+      </c>
+      <c r="C124" t="s">
+        <v>403</v>
+      </c>
+      <c r="D124" t="s">
+        <v>416</v>
+      </c>
+      <c r="E124" t="s">
+        <v>405</v>
+      </c>
+      <c r="F124" t="s">
+        <v>406</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I83" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I78">
-      <sortCondition ref="A1:A78"/>
+  <autoFilter ref="A1:I124" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I107">
+      <sortCondition ref="A1:A107"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
